--- a/Templates/RoomSched.xlsx
+++ b/Templates/RoomSched.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VibeCoding\UniGami WPF\UniversityScheduler_Csharp\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8CF17C1-7D0B-419C-9C1E-564C08690BFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1DAF29E-EB66-4D68-9EC2-A37D677C398D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -228,7 +228,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -241,14 +241,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="25">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -272,15 +266,89 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="medium">
-        <color auto="1"/>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -290,8 +358,8 @@
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="medium">
-        <color auto="1"/>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -305,8 +373,8 @@
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="medium">
-        <color auto="1"/>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -320,41 +388,21 @@
       <top style="medium">
         <color auto="1"/>
       </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom style="medium">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFF7EFFF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFF7EFFF"/>
       </bottom>
       <diagonal/>
     </border>
@@ -363,197 +411,10 @@
         <color auto="1"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFF7EFFF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFF7EFFF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFF7EFFF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFF7EFFF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFF7EFFF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFF7EFFF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFF7EFFF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFF7EFFF"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFF7EFFF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFF7EFFF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFF7EFFF"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFF7EFFF"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFF7EFFF"/>
+        <color indexed="64"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -562,66 +423,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -645,16 +449,43 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
@@ -944,481 +775,482 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:7" ht="18.75">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
     </row>
     <row r="3" spans="1:7" ht="18.75">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
     </row>
     <row r="4" spans="1:7" ht="18" customHeight="1">
-      <c r="A4" s="31" t="s">
+      <c r="A4" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="31"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
     </row>
     <row r="5" spans="1:7" ht="31.5">
-      <c r="A5" s="33" t="s">
+      <c r="A5" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="33"/>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="33"/>
-    </row>
-    <row r="7" spans="1:7" s="1" customFormat="1">
-      <c r="A7" s="2" t="s">
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+    </row>
+    <row r="6" spans="1:7" ht="15.75" thickBot="1"/>
+    <row r="7" spans="1:7" s="1" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A7" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="23" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="34"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="26"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="13"/>
+      <c r="B9" s="14"/>
       <c r="C9" s="14"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="35"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="27"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="35"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="27"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="37"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="35"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="27"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="35"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="27"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="35"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="27"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="35"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="27"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="35"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="27"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="35"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="27"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="35"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="27"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="8"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="35"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="27"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="12" t="s">
+      <c r="A19" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="15"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="35"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="27"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="35"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="27"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="35"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="27"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="35"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="27"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="12" t="s">
+      <c r="A23" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="35"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="27"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="12" t="s">
+      <c r="A24" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="35"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="27"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="12" t="s">
+      <c r="A25" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="35"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="27"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="12" t="s">
+      <c r="A26" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="35"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="27"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="12" t="s">
+      <c r="A27" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="15"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="35"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="27"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="12" t="s">
+      <c r="A28" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="35"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="27"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="12" t="s">
+      <c r="A29" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
-      <c r="G29" s="35"/>
+      <c r="B29" s="14"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="27"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="12" t="s">
+      <c r="A30" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="35"/>
+      <c r="B30" s="14"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="27"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="12" t="s">
+      <c r="A31" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="35"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="27"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="12" t="s">
+      <c r="A32" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="35"/>
+      <c r="B32" s="14"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="27"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="12" t="s">
+      <c r="A33" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="35"/>
+      <c r="B33" s="14"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="27"/>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="12" t="s">
+      <c r="A34" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="17"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="35"/>
+      <c r="B34" s="14"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="27"/>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="18" t="s">
+      <c r="A35" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="19"/>
-      <c r="C35" s="20"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="22"/>
-      <c r="F35" s="21"/>
-      <c r="G35" s="36"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="19"/>
     </row>
     <row r="37" spans="1:8" ht="18.75">
-      <c r="A37" s="23"/>
-      <c r="B37" s="24"/>
-      <c r="G37" s="25"/>
+      <c r="A37" s="2"/>
+      <c r="B37" s="3"/>
+      <c r="G37" s="4"/>
     </row>
     <row r="38" spans="1:8" ht="16.5">
-      <c r="A38" s="26"/>
-      <c r="B38" s="27"/>
-      <c r="G38" s="28"/>
+      <c r="A38" s="5"/>
+      <c r="B38" s="6"/>
+      <c r="G38" s="7"/>
     </row>
     <row r="39" spans="1:8" ht="16.5">
-      <c r="A39" s="26"/>
-      <c r="B39" s="27"/>
-      <c r="G39" s="28"/>
+      <c r="A39" s="5"/>
+      <c r="B39" s="6"/>
+      <c r="G39" s="7"/>
     </row>
     <row r="40" spans="1:8" ht="16.5">
-      <c r="A40" s="26"/>
-      <c r="B40" s="27"/>
-      <c r="G40" s="28"/>
+      <c r="A40" s="5"/>
+      <c r="B40" s="6"/>
+      <c r="G40" s="7"/>
     </row>
     <row r="41" spans="1:8" ht="16.5">
-      <c r="A41" s="26"/>
-      <c r="B41" s="27"/>
-      <c r="G41" s="28"/>
+      <c r="A41" s="5"/>
+      <c r="B41" s="6"/>
+      <c r="G41" s="7"/>
     </row>
     <row r="42" spans="1:8" ht="16.5">
-      <c r="A42" s="26"/>
-      <c r="B42" s="27"/>
-      <c r="G42" s="28"/>
+      <c r="A42" s="5"/>
+      <c r="B42" s="6"/>
+      <c r="G42" s="7"/>
     </row>
     <row r="43" spans="1:8" ht="16.5">
-      <c r="A43" s="26"/>
-      <c r="B43" s="27"/>
-      <c r="G43" s="28"/>
+      <c r="A43" s="5"/>
+      <c r="B43" s="6"/>
+      <c r="G43" s="7"/>
     </row>
     <row r="44" spans="1:8" ht="16.5">
-      <c r="A44" s="26"/>
-      <c r="B44" s="27"/>
-      <c r="G44" s="28"/>
+      <c r="A44" s="5"/>
+      <c r="B44" s="6"/>
+      <c r="G44" s="7"/>
     </row>
     <row r="45" spans="1:8" ht="16.5">
-      <c r="A45" s="26"/>
-      <c r="B45" s="27"/>
-      <c r="G45" s="28"/>
+      <c r="A45" s="5"/>
+      <c r="B45" s="6"/>
+      <c r="G45" s="7"/>
     </row>
     <row r="46" spans="1:8" ht="16.5">
-      <c r="A46" s="26"/>
-      <c r="B46" s="27"/>
-      <c r="G46" s="28"/>
+      <c r="A46" s="5"/>
+      <c r="B46" s="6"/>
+      <c r="G46" s="7"/>
     </row>
     <row r="47" spans="1:8" ht="16.5">
-      <c r="A47" s="26"/>
-      <c r="B47" s="27"/>
-      <c r="G47" s="28"/>
-      <c r="H47" s="29"/>
+      <c r="A47" s="5"/>
+      <c r="B47" s="6"/>
+      <c r="G47" s="7"/>
+      <c r="H47" s="8"/>
     </row>
     <row r="48" spans="1:8" ht="17.25">
-      <c r="A48" s="26"/>
-      <c r="B48" s="27"/>
-      <c r="G48" s="28"/>
-      <c r="H48" s="30"/>
+      <c r="A48" s="5"/>
+      <c r="B48" s="6"/>
+      <c r="G48" s="7"/>
+      <c r="H48" s="9"/>
     </row>
     <row r="49" spans="1:7" ht="16.5">
-      <c r="A49" s="26"/>
-      <c r="B49" s="27"/>
-      <c r="G49" s="28"/>
+      <c r="A49" s="5"/>
+      <c r="B49" s="6"/>
+      <c r="G49" s="7"/>
     </row>
     <row r="50" spans="1:7" ht="16.5">
-      <c r="A50" s="26"/>
-      <c r="B50" s="27"/>
-      <c r="G50" s="28"/>
+      <c r="A50" s="5"/>
+      <c r="B50" s="6"/>
+      <c r="G50" s="7"/>
     </row>
     <row r="51" spans="1:7" ht="16.5">
-      <c r="A51" s="26"/>
-      <c r="B51" s="27"/>
-      <c r="G51" s="28"/>
+      <c r="A51" s="5"/>
+      <c r="B51" s="6"/>
+      <c r="G51" s="7"/>
     </row>
     <row r="52" spans="1:7" ht="16.5">
-      <c r="A52" s="26"/>
-      <c r="B52" s="27"/>
-      <c r="G52" s="28"/>
+      <c r="A52" s="5"/>
+      <c r="B52" s="6"/>
+      <c r="G52" s="7"/>
     </row>
     <row r="53" spans="1:7" ht="16.5">
-      <c r="A53" s="26"/>
-      <c r="B53" s="27"/>
-      <c r="G53" s="28"/>
+      <c r="A53" s="5"/>
+      <c r="B53" s="6"/>
+      <c r="G53" s="7"/>
     </row>
     <row r="54" spans="1:7" ht="16.5">
-      <c r="A54" s="26"/>
-      <c r="B54" s="27"/>
-      <c r="G54" s="28"/>
+      <c r="A54" s="5"/>
+      <c r="B54" s="6"/>
+      <c r="G54" s="7"/>
     </row>
     <row r="55" spans="1:7" ht="16.5">
-      <c r="A55" s="26"/>
-      <c r="B55" s="27"/>
-      <c r="G55" s="28"/>
+      <c r="A55" s="5"/>
+      <c r="B55" s="6"/>
+      <c r="G55" s="7"/>
     </row>
     <row r="56" spans="1:7" ht="16.5">
-      <c r="A56" s="26"/>
-      <c r="B56" s="27"/>
-      <c r="G56" s="28"/>
+      <c r="A56" s="5"/>
+      <c r="B56" s="6"/>
+      <c r="G56" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="4">
